--- a/data/trans_orig/P36B02-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B02-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22865</t>
+          <t>24078</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45634</t>
+          <t>45421</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22680</t>
+          <t>21798</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45005</t>
+          <t>45723</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51829</t>
+          <t>51696</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84532</t>
+          <t>83249</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26016</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16418</t>
+          <t>16329</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17083</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37345</t>
+          <t>36669</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27345</t>
+          <t>27677</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50939</t>
+          <t>50758</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25915</t>
+          <t>25614</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49677</t>
+          <t>47114</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>59703</t>
+          <t>57754</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>93370</t>
+          <t>92029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37029</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63696</t>
+          <t>65369</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41520</t>
+          <t>40526</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70126</t>
+          <t>69812</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87372</t>
+          <t>87821</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127453</t>
+          <t>126842</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>874152</t>
+          <t>870393</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>915617</t>
+          <t>914616</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1160721</t>
+          <t>1162066</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1201353</t>
+          <t>1206571</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2044670</t>
+          <t>2047756</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2104276</t>
+          <t>2107819</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,82%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29765</t>
+          <t>29796</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58070</t>
+          <t>58072</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28921</t>
+          <t>29578</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54029</t>
+          <t>54286</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63959</t>
+          <t>65304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100567</t>
+          <t>102491</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11645</t>
+          <t>11702</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28830</t>
+          <t>29329</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11150</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29210</t>
+          <t>29851</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26863</t>
+          <t>26954</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52618</t>
+          <t>52275</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43190</t>
+          <t>43039</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74622</t>
+          <t>74024</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,39 +1656,39 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>40518</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>29625</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>54791</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>2,55%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>40518</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>29684</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>54856</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>1,87%</t>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>78153</t>
+          <t>80353</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>119544</t>
+          <t>119407</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74630</t>
+          <t>74051</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111171</t>
+          <t>109211</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74097</t>
+          <t>73211</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111073</t>
+          <t>110064</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>156825</t>
+          <t>157825</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>208558</t>
+          <t>208592</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1455661</t>
+          <t>1454607</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1511591</t>
+          <t>1508417</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1370085</t>
+          <t>1370092</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1419600</t>
+          <t>1421463</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2844711</t>
+          <t>2840267</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2916089</t>
+          <t>2912972</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,84%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15011</t>
+          <t>15621</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15936</t>
+          <t>14232</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>8347</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23409</t>
+          <t>24881</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1778</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13222</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26461</t>
+          <t>25435</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13640</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15223</t>
+          <t>15082</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34115</t>
+          <t>34690</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33390</t>
+          <t>33768</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>60230</t>
+          <t>59182</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12916</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30329</t>
+          <t>29911</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50837</t>
+          <t>50735</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>84436</t>
+          <t>81507</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>459726</t>
+          <t>460600</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>493344</t>
+          <t>492331</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>427180</t>
+          <t>429242</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>450819</t>
+          <t>450675</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>895217</t>
+          <t>896712</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>937757</t>
+          <t>937276</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,19%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65837</t>
+          <t>65148</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>102011</t>
+          <t>100961</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>63767</t>
+          <t>64531</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100214</t>
+          <t>100318</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>139340</t>
+          <t>137767</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>191227</t>
+          <t>187887</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28203</t>
+          <t>28068</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>53076</t>
+          <t>53346</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19633</t>
+          <t>18655</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42682</t>
+          <t>41151</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>53722</t>
+          <t>53829</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>86433</t>
+          <t>88060</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>92035</t>
+          <t>91048</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>135522</t>
+          <t>133429</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>67343</t>
+          <t>66896</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>103820</t>
+          <t>100065</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>167741</t>
+          <t>169238</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>222552</t>
+          <t>224056</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>161157</t>
+          <t>163167</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>213933</t>
+          <t>217172</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>142017</t>
+          <t>141782</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>191872</t>
+          <t>190166</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>319528</t>
+          <t>317973</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>393312</t>
+          <t>392374</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2816703</t>
+          <t>2815306</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2891869</t>
+          <t>2894300</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2982128</t>
+          <t>2981697</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3053318</t>
+          <t>3053397</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5822298</t>
+          <t>5823395</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5923989</t>
+          <t>5929839</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20929</t>
+          <t>20626</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45337</t>
+          <t>44514</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21537</t>
+          <t>21761</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43441</t>
+          <t>44329</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49067</t>
+          <t>47577</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81800</t>
+          <t>79735</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15781</t>
+          <t>15995</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>6665</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20891</t>
+          <t>21492</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12641</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31489</t>
+          <t>31705</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30548</t>
+          <t>30967</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57727</t>
+          <t>59287</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16332</t>
+          <t>15934</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36354</t>
+          <t>35215</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52938</t>
+          <t>54174</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>87723</t>
+          <t>88391</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19151</t>
+          <t>17627</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41306</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17065</t>
+          <t>17436</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37197</t>
+          <t>37972</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39759</t>
+          <t>40383</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71637</t>
+          <t>70323</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>839770</t>
+          <t>841697</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>882924</t>
+          <t>883593</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1222906</t>
+          <t>1221386</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1259687</t>
+          <t>1259030</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2076252</t>
+          <t>2075698</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2130730</t>
+          <t>2132573</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,3%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36770</t>
+          <t>36384</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65399</t>
+          <t>66779</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44949</t>
+          <t>44839</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75054</t>
+          <t>76557</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87448</t>
+          <t>88080</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131608</t>
+          <t>132390</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>10065</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29299</t>
+          <t>28248</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6806</t>
+          <t>6981</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22157</t>
+          <t>22509</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21557</t>
+          <t>20288</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46189</t>
+          <t>45911</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36627</t>
+          <t>36088</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64498</t>
+          <t>65043</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27657</t>
+          <t>28488</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55856</t>
+          <t>54668</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>71094</t>
+          <t>70415</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>111930</t>
+          <t>109350</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52622</t>
+          <t>52263</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85908</t>
+          <t>85422</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40266</t>
+          <t>40661</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69942</t>
+          <t>71808</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98832</t>
+          <t>101131</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>144301</t>
+          <t>145974</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1748953</t>
+          <t>1750013</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1804187</t>
+          <t>1804542</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1562287</t>
+          <t>1560426</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1614465</t>
+          <t>1611677</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3329980</t>
+          <t>3334670</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3405833</t>
+          <t>3404003</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,56%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>21265</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10476</t>
+          <t>10371</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30105</t>
+          <t>26955</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19898</t>
+          <t>20076</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42511</t>
+          <t>42600</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7449</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>941</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11490</t>
+          <t>12650</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23598</t>
+          <t>23394</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15319</t>
+          <t>15539</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12818</t>
+          <t>12849</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>32311</t>
+          <t>32184</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12356</t>
+          <t>11489</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28927</t>
+          <t>28428</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>5885</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21605</t>
+          <t>21020</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20921</t>
+          <t>19925</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44502</t>
+          <t>43003</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>418910</t>
+          <t>419557</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>446851</t>
+          <t>446652</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>404082</t>
+          <t>405091</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>429372</t>
+          <t>429631</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>832737</t>
+          <t>835039</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>870439</t>
+          <t>870695</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>74920</t>
+          <t>75848</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>116245</t>
+          <t>116331</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>87828</t>
+          <t>88549</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>130667</t>
+          <t>133776</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,47 +5788,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>200969</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>172730</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>228834</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>2,48%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>200969</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>174664</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>232131</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18956</t>
+          <t>19011</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42828</t>
+          <t>41672</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19494</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41547</t>
+          <t>41375</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>43628</t>
+          <t>41618</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>74887</t>
+          <t>72454</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>85844</t>
+          <t>84737</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>128557</t>
+          <t>125762</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>55200</t>
+          <t>56057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>91680</t>
+          <t>89774</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>149236</t>
+          <t>152118</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>207700</t>
+          <t>206294</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>93767</t>
+          <t>95470</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>137813</t>
+          <t>137511</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73419</t>
+          <t>73168</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>112243</t>
+          <t>112288</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>176181</t>
+          <t>176247</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>235933</t>
+          <t>235470</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3041669</t>
+          <t>3040416</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3115941</t>
+          <t>3114762</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3212661</t>
+          <t>3216732</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3281322</t>
+          <t>3286249</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6278460</t>
+          <t>6274278</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6381580</t>
+          <t>6379634</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15596</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34613</t>
+          <t>33168</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>8728</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24082</t>
+          <t>24292</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26252</t>
+          <t>27368</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51759</t>
+          <t>52068</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17424</t>
+          <t>17515</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>12246</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9394</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24448</t>
+          <t>24581</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23012</t>
+          <t>23778</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46920</t>
+          <t>46118</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13709</t>
+          <t>12960</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32528</t>
+          <t>32437</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>42990</t>
+          <t>41231</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73285</t>
+          <t>73299</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21460</t>
+          <t>21342</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43471</t>
+          <t>43444</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35693</t>
+          <t>35794</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63646</t>
+          <t>65318</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63710</t>
+          <t>64538</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>98153</t>
+          <t>100588</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>634381</t>
+          <t>634704</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>672675</t>
+          <t>671253</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>882690</t>
+          <t>883749</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>920158</t>
+          <t>921813</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1528738</t>
+          <t>1527807</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1582351</t>
+          <t>1583189</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,67%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55626</t>
+          <t>55642</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92458</t>
+          <t>88829</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36490</t>
+          <t>35515</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65393</t>
+          <t>63979</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>99070</t>
+          <t>99205</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141621</t>
+          <t>142796</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16332</t>
+          <t>16469</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37602</t>
+          <t>35946</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8737</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23202</t>
+          <t>24009</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29218</t>
+          <t>28809</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56238</t>
+          <t>56643</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69784</t>
+          <t>69564</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>108701</t>
+          <t>108129</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47019</t>
+          <t>47159</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79239</t>
+          <t>78384</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>125014</t>
+          <t>125316</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>174894</t>
+          <t>172865</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>131511</t>
+          <t>131665</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>180926</t>
+          <t>181535</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102935</t>
+          <t>102269</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>145839</t>
+          <t>146072</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>248192</t>
+          <t>248303</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>314683</t>
+          <t>312926</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1697416</t>
+          <t>1699339</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1766695</t>
+          <t>1767086</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1709524</t>
+          <t>1707683</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1768283</t>
+          <t>1766490</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3425796</t>
+          <t>3428677</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3518072</t>
+          <t>3520657</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,77%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>8720</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25619</t>
+          <t>27085</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16814</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36354</t>
+          <t>36014</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28497</t>
+          <t>29227</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55254</t>
+          <t>55039</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>932</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9193</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>888</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7964</t>
+          <t>7752</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12920</t>
+          <t>12596</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>5241</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18891</t>
+          <t>18648</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7224</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21464</t>
+          <t>22619</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15695</t>
+          <t>16117</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35638</t>
+          <t>35091</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29217</t>
+          <t>27778</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54525</t>
+          <t>54612</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36013</t>
+          <t>36014</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62529</t>
+          <t>62584</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71216</t>
+          <t>70046</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>110484</t>
+          <t>106970</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>458242</t>
+          <t>457845</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>492004</t>
+          <t>492544</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>441841</t>
+          <t>440844</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>475646</t>
+          <t>475080</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>909305</t>
+          <t>911915</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>958500</t>
+          <t>958513</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>88312</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129098</t>
+          <t>132217</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70363</t>
+          <t>71609</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>107039</t>
+          <t>108440</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>169621</t>
+          <t>170059</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>226153</t>
+          <t>226831</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26730</t>
+          <t>27339</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51565</t>
+          <t>53005</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>15061</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33462</t>
+          <t>33611</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>47752</t>
+          <t>46899</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>78347</t>
+          <t>78326</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>109207</t>
+          <t>110232</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>157535</t>
+          <t>154616</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>78054</t>
+          <t>78876</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>116637</t>
+          <t>116462</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>200491</t>
+          <t>197788</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>261535</t>
+          <t>259221</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>197927</t>
+          <t>200742</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>258161</t>
+          <t>256554</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>194071</t>
+          <t>191380</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>248961</t>
+          <t>251285</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>404749</t>
+          <t>407842</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>494736</t>
+          <t>489838</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2822640</t>
+          <t>2821815</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2906127</t>
+          <t>2905806</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3065953</t>
+          <t>3061322</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3142292</t>
+          <t>3138427</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5910293</t>
+          <t>5907452</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6025373</t>
+          <t>6026731</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,35%</t>
         </is>
       </c>
     </row>
@@ -9605,102 +9605,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22129</t>
+          <t>26406</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14471</t>
+          <t>17947</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31298</t>
+          <t>37813</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>33779</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>26122</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>43847</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,33%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>60184</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>46961</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>73083</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>4,3%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>30905</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>23822</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>39749</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>53034</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>42742</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>66001</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23691</t>
+          <t>25262</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16266</t>
+          <t>17236</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35291</t>
+          <t>37213</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15878</t>
+          <t>16057</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>10584</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23432</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>39569</t>
+          <t>41319</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29565</t>
+          <t>31546</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51490</t>
+          <t>53896</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32305</t>
+          <t>37014</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22502</t>
+          <t>26477</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43983</t>
+          <t>51822</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30938</t>
+          <t>36410</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23761</t>
+          <t>27916</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40110</t>
+          <t>46971</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>63244</t>
+          <t>73424</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>51171</t>
+          <t>57721</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>77161</t>
+          <t>89183</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68298</t>
+          <t>75319</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54814</t>
+          <t>59920</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84780</t>
+          <t>90836</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>128917</t>
+          <t>143698</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>113836</t>
+          <t>129200</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>146220</t>
+          <t>163800</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>197215</t>
+          <t>219017</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>177605</t>
+          <t>197647</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>218284</t>
+          <t>242640</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>368515</t>
+          <t>414528</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>352102</t>
+          <t>392021</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>389313</t>
+          <t>433903</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>548870</t>
+          <t>592095</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>529001</t>
+          <t>570529</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>566113</t>
+          <t>611145</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>917384</t>
+          <t>1006623</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>889925</t>
+          <t>975554</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>942386</t>
+          <t>1034844</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>73,89%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>111195</t>
+          <t>125070</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74771</t>
+          <t>101520</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142413</t>
+          <t>156680</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>88974</t>
+          <t>104553</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65791</t>
+          <t>86242</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>111515</t>
+          <t>124045</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>200169</t>
+          <t>229622</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157161</t>
+          <t>197600</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>240272</t>
+          <t>263004</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45650</t>
+          <t>50434</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30190</t>
+          <t>36516</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62474</t>
+          <t>67607</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>109709</t>
+          <t>45724</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36257</t>
+          <t>34960</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>348590</t>
+          <t>59159</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>155359</t>
+          <t>96158</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>79111</t>
+          <t>78286</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>453838</t>
+          <t>116750</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>98510</t>
+          <t>106448</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66680</t>
+          <t>85168</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>126345</t>
+          <t>134740</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>87391</t>
+          <t>94904</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62030</t>
+          <t>78880</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>107570</t>
+          <t>112099</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>185902</t>
+          <t>201352</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>145317</t>
+          <t>170107</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>222081</t>
+          <t>230100</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>357619</t>
+          <t>399206</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>248245</t>
+          <t>356046</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>415580</t>
+          <t>443031</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>330816</t>
+          <t>378410</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>239170</t>
+          <t>344873</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>378649</t>
+          <t>410667</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>688435</t>
+          <t>777617</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>543295</t>
+          <t>727627</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>774145</t>
+          <t>828930</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1677353</t>
+          <t>1549408</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1587493</t>
+          <t>1494690</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1872671</t>
+          <t>1597983</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1620933</t>
+          <t>1547802</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1477544</t>
+          <t>1511871</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1768970</t>
+          <t>1589682</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3298285</t>
+          <t>3097210</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3125799</t>
+          <t>3039782</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3531491</t>
+          <t>3164325</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>71,88%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>28141</t>
+          <t>29897</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18785</t>
+          <t>18382</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42476</t>
+          <t>44161</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>29370</t>
+          <t>34307</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22035</t>
+          <t>25643</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40082</t>
+          <t>45484</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>57511</t>
+          <t>64204</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44422</t>
+          <t>48996</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72727</t>
+          <t>80150</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15532</t>
+          <t>16773</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8418</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25674</t>
+          <t>28608</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14498</t>
+          <t>18167</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9475</t>
+          <t>11937</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21620</t>
+          <t>27434</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>30031</t>
+          <t>34941</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20583</t>
+          <t>24612</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43272</t>
+          <t>47735</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33297</t>
+          <t>33999</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23637</t>
+          <t>24340</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46796</t>
+          <t>47947</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23940</t>
+          <t>26325</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16574</t>
+          <t>18794</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33862</t>
+          <t>36856</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>57237</t>
+          <t>60324</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>44015</t>
+          <t>48205</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>73539</t>
+          <t>78232</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>106250</t>
+          <t>119810</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>87192</t>
+          <t>97944</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>128375</t>
+          <t>142689</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>76208</t>
+          <t>82639</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62684</t>
+          <t>66581</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>90945</t>
+          <t>96992</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>182458</t>
+          <t>202449</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>158384</t>
+          <t>175931</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>207881</t>
+          <t>229118</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>463402</t>
+          <t>511107</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>439063</t>
+          <t>485845</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>487197</t>
+          <t>537595</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,32 +11456,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>516447</t>
+          <t>573439</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>496358</t>
+          <t>553140</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>534082</t>
+          <t>593084</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>979849</t>
+          <t>1084546</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>950384</t>
+          <t>1053315</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1008575</t>
+          <t>1120342</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,45%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>161465</t>
+          <t>181373</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>123669</t>
+          <t>153421</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>194263</t>
+          <t>215560</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>149249</t>
+          <t>172638</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121613</t>
+          <t>149786</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>175427</t>
+          <t>196772</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>310715</t>
+          <t>354011</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>268534</t>
+          <t>317475</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>357718</t>
+          <t>395010</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>84874</t>
+          <t>92469</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>64512</t>
+          <t>75053</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>106877</t>
+          <t>115776</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>140085</t>
+          <t>79948</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>67091</t>
+          <t>65164</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>381610</t>
+          <t>96028</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>224959</t>
+          <t>172417</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>148865</t>
+          <t>148386</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>462642</t>
+          <t>202184</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -11877,67 +11877,67 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>164113</t>
+          <t>177461</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>127370</t>
+          <t>150225</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>196087</t>
+          <t>209435</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>4,27%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>5,95%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>157639</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>137727</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>180773</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
           <t>3,69%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>142269</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>115485</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>166285</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>306382</t>
+          <t>335100</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>259583</t>
+          <t>298545</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>352006</t>
+          <t>373210</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>532167</t>
+          <t>594336</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>416841</t>
+          <t>544400</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>599308</t>
+          <t>643012</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>535941</t>
+          <t>604746</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>436725</t>
+          <t>564140</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>589015</t>
+          <t>644697</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1068108</t>
+          <t>1199082</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>935621</t>
+          <t>1137419</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1161244</t>
+          <t>1264709</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2509271</t>
+          <t>2475044</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2414356</t>
+          <t>2416679</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2723339</t>
+          <t>2529683</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2686249</t>
+          <t>2713336</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2550021</t>
+          <t>2663764</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2830070</t>
+          <t>2764016</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5195520</t>
+          <t>5188380</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5026176</t>
+          <t>5104369</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5424334</t>
+          <t>5261654</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>72,58%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
